--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +806,118 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129766791</v>
+      </c>
+      <c r="B3" t="n">
+        <v>105747</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>598058</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6364881</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105747</v>
+        <v>105752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105752</v>
+        <v>105756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105756</v>
+        <v>105758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105758</v>
+        <v>105768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -919,6 +919,103 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129943349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>100979</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>598271</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6364960</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105768</v>
+        <v>105772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>129943349</v>
       </c>
       <c r="B4" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105772</v>
+        <v>105775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>129943349</v>
       </c>
       <c r="B4" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105775</v>
+        <v>105776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>129943349</v>
       </c>
       <c r="B4" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>129766791</v>
       </c>
       <c r="B3" t="n">
-        <v>105776</v>
+        <v>105793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
         <v>129943349</v>
       </c>
       <c r="B4" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>129943349</v>
       </c>
       <c r="B4" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -924,7 +924,7 @@
         <v>129943349</v>
       </c>
       <c r="B4" t="n">
-        <v>101022</v>
+        <v>101109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -812,7 +812,7 @@
         <v>134236167</v>
       </c>
       <c r="B3" t="n">
-        <v>106222</v>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,7 +914,7 @@
         <v>134236371</v>
       </c>
       <c r="B4" t="n">
-        <v>101389</v>
+        <v>101396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>727567</v>
       </c>
       <c r="B2" t="n">
-        <v>93131</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598278.675785602</v>
+        <v>598279</v>
       </c>
       <c r="R2" t="n">
-        <v>6364902.44921601</v>
+        <v>6364902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2007-08-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-08-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -809,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134236167</v>
+        <v>134235919</v>
       </c>
       <c r="B3" t="n">
-        <v>106229</v>
+        <v>4937</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>100217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Tvåfläckig praktbagge</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Agrilus biguttatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1777)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -844,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598058</v>
+        <v>598374</v>
       </c>
       <c r="R3" t="n">
-        <v>6364881</v>
+        <v>6364889</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -874,17 +859,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Fåtal</t>
+          <t>Tvåfläckig praktbagge</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,32 +896,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134236371</v>
+        <v>134235918</v>
       </c>
       <c r="B4" t="n">
-        <v>101396</v>
+        <v>7171</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>101783</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåtandad plattbagge</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Silvanus bidentatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fabricius, 1792)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598271</v>
+        <v>598290</v>
       </c>
       <c r="R4" t="n">
-        <v>6364960</v>
+        <v>6364837</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -976,17 +961,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2024-06-13</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåtandad plattbagge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,6 +995,1332 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134236115</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58698</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>598013</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6364833</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sjungande i hygge/ gles skog</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134236479</v>
+      </c>
+      <c r="B6" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>598268</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6364994</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134236140</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>598232</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6364949</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134236141</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598177</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6364930</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134236142</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>598374</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6364802</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134236167</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>598058</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6364881</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fåtal</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>134236168</v>
+      </c>
+      <c r="B11" t="n">
+        <v>106236</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>598028</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6364884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fåtal</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134236325</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>598050</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6364907</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Riklig</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134236371</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>598271</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6364960</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134236372</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>598237</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6364942</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134236373</v>
+      </c>
+      <c r="B15" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>598352</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6364894</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134236375</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>598336</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6364888</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134236376</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Oskarshamns kommun, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>598373</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6364800</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Misterhult</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sofie Alveteg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mikael Molander</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33241-2022 artfynd.xlsx
+++ b/artfynd/A 33241-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
           <t>Andersson, M. Utredningsobj. H-län 2007</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/727567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134235919</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134235918</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236115</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236479</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236140</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236141</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,6 +1545,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236142</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1607,6 +1652,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236167</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1709,6 +1759,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236168</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1811,6 +1866,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236325</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1913,6 +1973,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236371</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2015,6 +2080,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236372</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2117,6 +2187,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236373</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2219,6 +2294,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236375</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,8 +2401,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134236376</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>